--- a/Practical_classes/2025_student_projects/student_projects_overview.xlsx
+++ b/Practical_classes/2025_student_projects/student_projects_overview.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keil\Dropbox\GitHub\Spatial-Ecology-and-Macroecology\Practical_classes\2025_student_projects\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\keil\Dropbox\GitHub\Spatial-Ecology-and-Macroecology\Practical_classes\2025_student_projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546F319C-016F-4C5D-980C-DF309A952FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B9523A-C879-4633-A0B1-3B21638F5913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>Adam</t>
   </si>
@@ -100,6 +100,96 @@
   </si>
   <si>
     <t>Hypothesis</t>
+  </si>
+  <si>
+    <t>Kamzík horský</t>
+  </si>
+  <si>
+    <t>Chamoix distribution</t>
+  </si>
+  <si>
+    <t>Elevation, land cover, maybe aspect or slope, teplota, srazky</t>
+  </si>
+  <si>
+    <t>Platypus</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Platypus distribution</t>
+  </si>
+  <si>
+    <t>Dry season precipitation, some water body/stream, protected area, elevation, temperature</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Lizard Teira dugesii</t>
+  </si>
+  <si>
+    <t>Madeira</t>
+  </si>
+  <si>
+    <t>Temperature, precipitation, elevation, seasonality, rocks/bare ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crested tit </t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Land cover (coniferous forests), human density, climate contientality</t>
+  </si>
+  <si>
+    <t>Buteo rufinus</t>
+  </si>
+  <si>
+    <t>Central Asia</t>
+  </si>
+  <si>
+    <t>Temperature, global landc cover with open habitat, precipitation, elevation</t>
+  </si>
+  <si>
+    <t>Lyrurus tetrix</t>
+  </si>
+  <si>
+    <t>Elevation, landcover (les vs neles), human density, protected area</t>
+  </si>
+  <si>
+    <t>Lagopus leucura</t>
+  </si>
+  <si>
+    <t>North America</t>
+  </si>
+  <si>
+    <t>Land cover, elevation, precipitation, human density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petr </t>
+  </si>
+  <si>
+    <t>Keil</t>
+  </si>
+  <si>
+    <t>Rock hyrax</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
+    <t>Biome, rocks, elevation, precipitation, temperature</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Marten</t>
+  </si>
+  <si>
+    <t>Elevation, human index, climate</t>
   </si>
 </sst>
 </file>
@@ -435,19 +525,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" customWidth="1"/>
+    <col min="8" max="8" width="31.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -476,87 +566,200 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>